--- a/podium_highlighted.xlsx
+++ b/podium_highlighted.xlsx
@@ -86,7 +86,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -125,6 +125,9 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -915,7 +918,7 @@
           <t>6630</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>9855</t>
         </is>
@@ -1081,7 +1084,7 @@
           <t>9763</t>
         </is>
       </c>
-      <c r="R23" s="14" t="inlineStr">
+      <c r="R23" s="7" t="inlineStr">
         <is>
           <t>9744</t>
         </is>
@@ -1393,7 +1396,7 @@
           <t>9110</t>
         </is>
       </c>
-      <c r="M33" s="14" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>6440</t>
         </is>
@@ -1413,7 +1416,7 @@
           <t>5430</t>
         </is>
       </c>
-      <c r="R33" s="14" t="inlineStr">
+      <c r="R33" s="7" t="inlineStr">
         <is>
           <t>6440</t>
         </is>
@@ -1720,7 +1723,7 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="L43" s="14" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>9920</t>
         </is>
@@ -1906,7 +1909,7 @@
           <t>9650</t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t>6400</t>
         </is>
@@ -2052,7 +2055,7 @@
           <t>8741</t>
         </is>
       </c>
-      <c r="L53" s="14" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
@@ -2911,7 +2914,7 @@
           <t>8643</t>
         </is>
       </c>
-      <c r="F73" s="14" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>7764</t>
         </is>
@@ -2951,7 +2954,7 @@
           <t>7433</t>
         </is>
       </c>
-      <c r="Q73" s="14" t="inlineStr">
+      <c r="Q73" s="7" t="inlineStr">
         <is>
           <t>7742</t>
         </is>
@@ -3107,7 +3110,7 @@
       </c>
     </row>
     <row r="80" ht="14.25" customHeight="1" s="6">
-      <c r="H80" s="7" t="inlineStr">
+      <c r="H80" s="15" t="inlineStr">
         <is>
           <t>6550</t>
         </is>
@@ -3117,7 +3120,7 @@
           <t>7531</t>
         </is>
       </c>
-      <c r="J80" s="7" t="inlineStr">
+      <c r="J80" s="15" t="inlineStr">
         <is>
           <t>8633</t>
         </is>
@@ -3127,7 +3130,7 @@
           <t>2200</t>
         </is>
       </c>
-      <c r="M80" s="7" t="inlineStr">
+      <c r="M80" s="15" t="inlineStr">
         <is>
           <t>9975</t>
         </is>
@@ -3142,12 +3145,12 @@
           <t>9972</t>
         </is>
       </c>
-      <c r="Q80" s="7" t="inlineStr">
+      <c r="Q80" s="15" t="inlineStr">
         <is>
           <t>9443</t>
         </is>
       </c>
-      <c r="R80" s="7" t="inlineStr">
+      <c r="R80" s="15" t="inlineStr">
         <is>
           <t>8440</t>
         </is>
@@ -3263,7 +3266,7 @@
           <t>5431</t>
         </is>
       </c>
-      <c r="L83" s="14" t="inlineStr">
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
@@ -3273,7 +3276,7 @@
           <t>8421</t>
         </is>
       </c>
-      <c r="N83" s="14" t="inlineStr">
+      <c r="N83" s="7" t="inlineStr">
         <is>
           <t>8831</t>
         </is>
@@ -3499,7 +3502,7 @@
           <t>7333</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
+      <c r="F89" s="15" t="inlineStr">
         <is>
           <t>9953</t>
         </is>
@@ -3891,7 +3894,7 @@
           <t>8742</t>
         </is>
       </c>
-      <c r="N99" s="7" t="inlineStr">
+      <c r="N99" s="15" t="inlineStr">
         <is>
           <t>6400</t>
         </is>
@@ -4213,7 +4216,7 @@
           <t>9621</t>
         </is>
       </c>
-      <c r="L109" s="7" t="inlineStr">
+      <c r="L109" s="15" t="inlineStr">
         <is>
           <t>5520</t>
         </is>
@@ -4709,7 +4712,7 @@
           <t>3210</t>
         </is>
       </c>
-      <c r="M122" s="14" t="inlineStr">
+      <c r="M122" s="7" t="inlineStr">
         <is>
           <t>2220</t>
         </is>
@@ -5030,7 +5033,7 @@
           <t>7541</t>
         </is>
       </c>
-      <c r="J131" s="14" t="inlineStr">
+      <c r="J131" s="7" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
@@ -5050,7 +5053,7 @@
           <t>6422</t>
         </is>
       </c>
-      <c r="P131" s="14" t="inlineStr">
+      <c r="P131" s="7" t="inlineStr">
         <is>
           <t>8840</t>
         </is>
@@ -5377,7 +5380,7 @@
           <t>6533</t>
         </is>
       </c>
-      <c r="N141" s="14" t="inlineStr">
+      <c r="N141" s="7" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
@@ -5553,7 +5556,7 @@
           <t>9864</t>
         </is>
       </c>
-      <c r="J148" s="7" t="inlineStr">
+      <c r="J148" s="15" t="inlineStr">
         <is>
           <t>8644</t>
         </is>
@@ -5563,7 +5566,7 @@
           <t>7431</t>
         </is>
       </c>
-      <c r="M148" s="7" t="inlineStr">
+      <c r="M148" s="15" t="inlineStr">
         <is>
           <t>9551</t>
         </is>
@@ -5684,17 +5687,17 @@
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1" s="6">
-      <c r="H151" s="14" t="inlineStr">
+      <c r="H151" s="7" t="inlineStr">
         <is>
           <t>8666</t>
         </is>
       </c>
-      <c r="I151" s="14" t="inlineStr">
+      <c r="I151" s="7" t="inlineStr">
         <is>
           <t>8411</t>
         </is>
       </c>
-      <c r="J151" s="14" t="inlineStr">
+      <c r="J151" s="7" t="inlineStr">
         <is>
           <t>8831</t>
         </is>
@@ -5880,7 +5883,7 @@
           <t>7540</t>
         </is>
       </c>
-      <c r="I158" s="7" t="inlineStr">
+      <c r="I158" s="15" t="inlineStr">
         <is>
           <t>7522</t>
         </is>
@@ -6242,7 +6245,7 @@
           <t>9763</t>
         </is>
       </c>
-      <c r="Q168" s="7" t="inlineStr">
+      <c r="Q168" s="15" t="inlineStr">
         <is>
           <t>4420</t>
         </is>
@@ -6363,7 +6366,7 @@
           <t>9331</t>
         </is>
       </c>
-      <c r="L171" s="14" t="inlineStr">
+      <c r="L171" s="7" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
@@ -6685,7 +6688,7 @@
           <t>9771</t>
         </is>
       </c>
-      <c r="I181" s="14" t="inlineStr">
+      <c r="I181" s="7" t="inlineStr">
         <is>
           <t>8633</t>
         </is>
@@ -6700,7 +6703,7 @@
           <t>6300</t>
         </is>
       </c>
-      <c r="M181" s="14" t="inlineStr">
+      <c r="M181" s="7" t="inlineStr">
         <is>
           <t>9951</t>
         </is>
@@ -7032,7 +7035,7 @@
           <t>9872</t>
         </is>
       </c>
-      <c r="M191" s="14" t="inlineStr">
+      <c r="M191" s="7" t="inlineStr">
         <is>
           <t>7522</t>
         </is>
@@ -7363,7 +7366,7 @@
           <t>9855</t>
         </is>
       </c>
-      <c r="I201" s="14" t="inlineStr">
+      <c r="I201" s="7" t="inlineStr">
         <is>
           <t>8411</t>
         </is>
@@ -7594,7 +7597,7 @@
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1" s="6">
-      <c r="D208" s="7" t="inlineStr">
+      <c r="D208" s="15" t="inlineStr">
         <is>
           <t>9940</t>
         </is>
@@ -7810,7 +7813,7 @@
           <t>9410</t>
         </is>
       </c>
-      <c r="P211" s="14" t="inlineStr">
+      <c r="P211" s="7" t="inlineStr">
         <is>
           <t>8862</t>
         </is>
@@ -7996,12 +7999,12 @@
           <t>8653</t>
         </is>
       </c>
-      <c r="I218" s="7" t="inlineStr">
+      <c r="I218" s="15" t="inlineStr">
         <is>
           <t>5100</t>
         </is>
       </c>
-      <c r="J218" s="7" t="inlineStr">
+      <c r="J218" s="15" t="inlineStr">
         <is>
           <t>8833</t>
         </is>
@@ -8137,12 +8140,12 @@
           <t>9411</t>
         </is>
       </c>
-      <c r="I221" s="14" t="inlineStr">
+      <c r="I221" s="7" t="inlineStr">
         <is>
           <t>7731</t>
         </is>
       </c>
-      <c r="J221" s="14" t="inlineStr">
+      <c r="J221" s="7" t="inlineStr">
         <is>
           <t>8851</t>
         </is>
@@ -8157,7 +8160,7 @@
           <t>9862</t>
         </is>
       </c>
-      <c r="N221" s="14" t="inlineStr">
+      <c r="N221" s="7" t="inlineStr">
         <is>
           <t>6653</t>
         </is>
@@ -8358,12 +8361,12 @@
           <t>7743</t>
         </is>
       </c>
-      <c r="Q228" s="7" t="inlineStr">
+      <c r="Q228" s="15" t="inlineStr">
         <is>
           <t>9975</t>
         </is>
       </c>
-      <c r="R228" s="7" t="inlineStr">
+      <c r="R228" s="15" t="inlineStr">
         <is>
           <t>8862</t>
         </is>
@@ -8469,12 +8472,12 @@
           <t>8520</t>
         </is>
       </c>
-      <c r="I231" s="14" t="inlineStr">
+      <c r="I231" s="7" t="inlineStr">
         <is>
           <t>8853</t>
         </is>
       </c>
-      <c r="J231" s="14" t="inlineStr">
+      <c r="J231" s="7" t="inlineStr">
         <is>
           <t>9663</t>
         </is>
@@ -9032,7 +9035,7 @@
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1" s="6">
-      <c r="D248" s="7" t="inlineStr">
+      <c r="D248" s="15" t="inlineStr">
         <is>
           <t>9722</t>
         </is>
@@ -9580,7 +9583,7 @@
           <t>5522</t>
         </is>
       </c>
-      <c r="P261" s="14" t="inlineStr">
+      <c r="P261" s="7" t="inlineStr">
         <is>
           <t>6664</t>
         </is>
@@ -9761,7 +9764,7 @@
           <t>7321</t>
         </is>
       </c>
-      <c r="M268" s="7" t="inlineStr">
+      <c r="M268" s="15" t="inlineStr">
         <is>
           <t>5520</t>
         </is>
@@ -9892,7 +9895,7 @@
           <t>9952</t>
         </is>
       </c>
-      <c r="J271" s="14" t="inlineStr">
+      <c r="J271" s="7" t="inlineStr">
         <is>
           <t>9533</t>
         </is>
@@ -9912,7 +9915,7 @@
           <t>9872</t>
         </is>
       </c>
-      <c r="P271" s="14" t="inlineStr">
+      <c r="P271" s="7" t="inlineStr">
         <is>
           <t>8110</t>
         </is>
@@ -10078,7 +10081,7 @@
           <t>6410</t>
         </is>
       </c>
-      <c r="I278" s="7" t="inlineStr">
+      <c r="I278" s="15" t="inlineStr">
         <is>
           <t>8422</t>
         </is>
@@ -10239,12 +10242,12 @@
           <t>8632</t>
         </is>
       </c>
-      <c r="N281" s="14" t="inlineStr">
+      <c r="N281" s="7" t="inlineStr">
         <is>
           <t>8875</t>
         </is>
       </c>
-      <c r="P281" s="14" t="inlineStr">
+      <c r="P281" s="7" t="inlineStr">
         <is>
           <t>9553</t>
         </is>
@@ -10550,7 +10553,7 @@
           <t>9650</t>
         </is>
       </c>
-      <c r="I290" s="14" t="inlineStr">
+      <c r="I290" s="7" t="inlineStr">
         <is>
           <t>8840</t>
         </is>
@@ -10917,7 +10920,7 @@
           <t>9876</t>
         </is>
       </c>
-      <c r="R300" s="8" t="inlineStr">
+      <c r="R300" s="7" t="inlineStr">
         <is>
           <t>9644</t>
         </is>
@@ -11465,12 +11468,12 @@
           <t>9766</t>
         </is>
       </c>
-      <c r="I317" s="7" t="inlineStr">
+      <c r="I317" s="15" t="inlineStr">
         <is>
           <t>6400</t>
         </is>
       </c>
-      <c r="J317" s="7" t="inlineStr">
+      <c r="J317" s="15" t="inlineStr">
         <is>
           <t>9722</t>
         </is>
@@ -11651,7 +11654,7 @@
           <t>3220</t>
         </is>
       </c>
-      <c r="M320" s="14" t="inlineStr">
+      <c r="M320" s="7" t="inlineStr">
         <is>
           <t>9511</t>
         </is>
@@ -11822,12 +11825,12 @@
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1" s="6">
-      <c r="H327" s="7" t="inlineStr">
+      <c r="H327" s="15" t="inlineStr">
         <is>
           <t>7533</t>
         </is>
       </c>
-      <c r="I327" s="7" t="inlineStr">
+      <c r="I327" s="15" t="inlineStr">
         <is>
           <t>6600</t>
         </is>
@@ -11837,12 +11840,12 @@
           <t>9760</t>
         </is>
       </c>
-      <c r="L327" s="7" t="inlineStr">
+      <c r="L327" s="15" t="inlineStr">
         <is>
           <t>8842</t>
         </is>
       </c>
-      <c r="M327" s="7" t="inlineStr">
+      <c r="M327" s="15" t="inlineStr">
         <is>
           <t>5100</t>
         </is>
@@ -11963,7 +11966,7 @@
       </c>
     </row>
     <row r="330" ht="14.25" customHeight="1" s="6">
-      <c r="H330" s="14" t="inlineStr">
+      <c r="H330" s="7" t="inlineStr">
         <is>
           <t>6653</t>
         </is>
@@ -11993,7 +11996,7 @@
           <t>9852</t>
         </is>
       </c>
-      <c r="P330" s="14" t="inlineStr">
+      <c r="P330" s="7" t="inlineStr">
         <is>
           <t>6400</t>
         </is>
@@ -12305,7 +12308,7 @@
           <t>9332</t>
         </is>
       </c>
-      <c r="J340" s="14" t="inlineStr">
+      <c r="J340" s="7" t="inlineStr">
         <is>
           <t>8622</t>
         </is>
@@ -12315,7 +12318,7 @@
           <t>7643</t>
         </is>
       </c>
-      <c r="M340" s="14" t="inlineStr">
+      <c r="M340" s="7" t="inlineStr">
         <is>
           <t>8400</t>
         </is>
@@ -12516,7 +12519,7 @@
           <t>9930</t>
         </is>
       </c>
-      <c r="P347" s="7" t="inlineStr">
+      <c r="P347" s="15" t="inlineStr">
         <is>
           <t>9973</t>
         </is>
@@ -12662,7 +12665,7 @@
           <t>8210</t>
         </is>
       </c>
-      <c r="Q350" s="14" t="inlineStr">
+      <c r="Q350" s="7" t="inlineStr">
         <is>
           <t>4431</t>
         </is>
@@ -12858,7 +12861,7 @@
           <t>8776</t>
         </is>
       </c>
-      <c r="R357" s="7" t="inlineStr">
+      <c r="R357" s="15" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
@@ -12979,7 +12982,7 @@
           <t>8752</t>
         </is>
       </c>
-      <c r="M360" s="14" t="inlineStr">
+      <c r="M360" s="7" t="inlineStr">
         <is>
           <t>8840</t>
         </is>
@@ -13165,7 +13168,7 @@
           <t>9742</t>
         </is>
       </c>
-      <c r="L367" s="7" t="inlineStr">
+      <c r="L367" s="15" t="inlineStr">
         <is>
           <t>7511</t>
         </is>
@@ -13301,7 +13304,7 @@
           <t>9862</t>
         </is>
       </c>
-      <c r="J370" s="14" t="inlineStr">
+      <c r="J370" s="7" t="inlineStr">
         <is>
           <t>8880</t>
         </is>
@@ -13819,7 +13822,7 @@
           <t>7650</t>
         </is>
       </c>
-      <c r="I387" s="7" t="inlineStr">
+      <c r="I387" s="15" t="inlineStr">
         <is>
           <t>8550</t>
         </is>
@@ -13955,7 +13958,7 @@
       </c>
     </row>
     <row r="390" ht="14.25" customHeight="1" s="6">
-      <c r="H390" s="14" t="inlineStr">
+      <c r="H390" s="7" t="inlineStr">
         <is>
           <t>8800</t>
         </is>
@@ -14156,7 +14159,7 @@
           <t>7531</t>
         </is>
       </c>
-      <c r="J397" s="7" t="inlineStr">
+      <c r="J397" s="15" t="inlineStr">
         <is>
           <t>9544</t>
         </is>
@@ -14302,7 +14305,7 @@
           <t>9860</t>
         </is>
       </c>
-      <c r="L400" s="14" t="inlineStr">
+      <c r="L400" s="7" t="inlineStr">
         <is>
           <t>8440</t>
         </is>
@@ -14317,17 +14320,17 @@
           <t>9521</t>
         </is>
       </c>
-      <c r="P400" s="14" t="inlineStr">
+      <c r="P400" s="7" t="inlineStr">
         <is>
           <t>4211</t>
         </is>
       </c>
-      <c r="Q400" s="14" t="inlineStr">
+      <c r="Q400" s="7" t="inlineStr">
         <is>
           <t>9700</t>
         </is>
       </c>
-      <c r="R400" s="14" t="inlineStr">
+      <c r="R400" s="7" t="inlineStr">
         <is>
           <t>8875</t>
         </is>
@@ -14493,7 +14496,7 @@
           <t>6432</t>
         </is>
       </c>
-      <c r="L407" s="7" t="inlineStr">
+      <c r="L407" s="15" t="inlineStr">
         <is>
           <t>9544</t>
         </is>
@@ -14508,7 +14511,7 @@
           <t>5321</t>
         </is>
       </c>
-      <c r="P407" s="7" t="inlineStr">
+      <c r="P407" s="15" t="inlineStr">
         <is>
           <t>9553</t>
         </is>
@@ -14518,7 +14521,7 @@
           <t>6432</t>
         </is>
       </c>
-      <c r="R407" s="7" t="inlineStr">
+      <c r="R407" s="15" t="inlineStr">
         <is>
           <t>5500</t>
         </is>
@@ -14810,7 +14813,7 @@
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1" s="6">
-      <c r="H417" s="7" t="inlineStr">
+      <c r="H417" s="15" t="inlineStr">
         <is>
           <t>8864</t>
         </is>
@@ -14991,7 +14994,7 @@
           <t>6500</t>
         </is>
       </c>
-      <c r="R420" s="14" t="inlineStr">
+      <c r="R420" s="7" t="inlineStr">
         <is>
           <t>9221</t>
         </is>
@@ -15227,7 +15230,7 @@
           <t>9998</t>
         </is>
       </c>
-      <c r="N427" s="7" t="inlineStr">
+      <c r="N427" s="15" t="inlineStr">
         <is>
           <t>7311</t>
         </is>
@@ -15373,7 +15376,7 @@
           <t>9960</t>
         </is>
       </c>
-      <c r="H430" s="14" t="inlineStr">
+      <c r="H430" s="7" t="inlineStr">
         <is>
           <t>7441</t>
         </is>
@@ -15388,7 +15391,7 @@
           <t>8742</t>
         </is>
       </c>
-      <c r="L430" s="14" t="inlineStr">
+      <c r="L430" s="7" t="inlineStr">
         <is>
           <t>9744</t>
         </is>
@@ -15704,7 +15707,7 @@
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1" s="6">
-      <c r="H439" s="14" t="inlineStr">
+      <c r="H439" s="7" t="inlineStr">
         <is>
           <t>8840</t>
         </is>
@@ -15734,7 +15737,7 @@
           <t>9652</t>
         </is>
       </c>
-      <c r="P439" s="14" t="inlineStr">
+      <c r="P439" s="7" t="inlineStr">
         <is>
           <t>9441</t>
         </is>
@@ -15910,7 +15913,7 @@
           <t>9621</t>
         </is>
       </c>
-      <c r="L446" s="7" t="inlineStr">
+      <c r="L446" s="15" t="inlineStr">
         <is>
           <t>9771</t>
         </is>
@@ -16066,7 +16069,7 @@
           <t>9750</t>
         </is>
       </c>
-      <c r="P449" s="14" t="inlineStr">
+      <c r="P449" s="7" t="inlineStr">
         <is>
           <t>7755</t>
         </is>
@@ -16558,7 +16561,7 @@
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1" s="6">
-      <c r="H466" s="7" t="inlineStr">
+      <c r="H466" s="15" t="inlineStr">
         <is>
           <t>6220</t>
         </is>
@@ -16588,7 +16591,7 @@
           <t>9541</t>
         </is>
       </c>
-      <c r="P466" s="7" t="inlineStr">
+      <c r="P466" s="15" t="inlineStr">
         <is>
           <t>9744</t>
         </is>
@@ -16699,7 +16702,7 @@
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1" s="6">
-      <c r="H469" s="14" t="inlineStr">
+      <c r="H469" s="7" t="inlineStr">
         <is>
           <t>5520</t>
         </is>
@@ -16724,12 +16727,12 @@
           <t>4330</t>
         </is>
       </c>
-      <c r="N469" s="14" t="inlineStr">
+      <c r="N469" s="7" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
       </c>
-      <c r="P469" s="14" t="inlineStr">
+      <c r="P469" s="7" t="inlineStr">
         <is>
           <t>8442</t>
         </is>
@@ -17052,12 +17055,12 @@
           <t>8620</t>
         </is>
       </c>
-      <c r="M480" s="14" t="inlineStr">
+      <c r="M480" s="7" t="inlineStr">
         <is>
           <t>8851</t>
         </is>
       </c>
-      <c r="N480" s="14" t="inlineStr">
+      <c r="N480" s="7" t="inlineStr">
         <is>
           <t>9663</t>
         </is>
@@ -17227,7 +17230,7 @@
           <t>7321</t>
         </is>
       </c>
-      <c r="I486" s="7" t="inlineStr">
+      <c r="I486" s="15" t="inlineStr">
         <is>
           <t>8772</t>
         </is>
@@ -17388,7 +17391,7 @@
           <t>9981</t>
         </is>
       </c>
-      <c r="N489" s="14" t="inlineStr">
+      <c r="N489" s="7" t="inlineStr">
         <is>
           <t>8877</t>
         </is>
@@ -17594,7 +17597,7 @@
           <t>9321</t>
         </is>
       </c>
-      <c r="R496" s="7" t="inlineStr">
+      <c r="R496" s="15" t="inlineStr">
         <is>
           <t>7742</t>
         </is>
@@ -17695,7 +17698,7 @@
       </c>
     </row>
     <row r="499" ht="14.25" customHeight="1" s="6">
-      <c r="H499" s="14" t="inlineStr">
+      <c r="H499" s="7" t="inlineStr">
         <is>
           <t>6330</t>
         </is>
@@ -18052,7 +18055,7 @@
           <t>7553</t>
         </is>
       </c>
-      <c r="N509" s="14" t="inlineStr">
+      <c r="N509" s="7" t="inlineStr">
         <is>
           <t>6433</t>
         </is>
@@ -18282,7 +18285,7 @@
           <t>8310</t>
         </is>
       </c>
-      <c r="I515" s="7" t="inlineStr">
+      <c r="I515" s="15" t="inlineStr">
         <is>
           <t>8440</t>
         </is>
@@ -18302,7 +18305,7 @@
           <t>7632</t>
         </is>
       </c>
-      <c r="N515" s="7" t="inlineStr">
+      <c r="N515" s="15" t="inlineStr">
         <is>
           <t>7731</t>
         </is>
@@ -18317,7 +18320,7 @@
           <t>7651</t>
         </is>
       </c>
-      <c r="R515" s="7" t="inlineStr">
+      <c r="R515" s="15" t="inlineStr">
         <is>
           <t>6422</t>
         </is>
@@ -18448,17 +18451,17 @@
           <t>9764</t>
         </is>
       </c>
-      <c r="H518" s="14" t="inlineStr">
+      <c r="H518" s="7" t="inlineStr">
         <is>
           <t>7500</t>
         </is>
       </c>
-      <c r="I518" s="14" t="inlineStr">
+      <c r="I518" s="7" t="inlineStr">
         <is>
           <t>9522</t>
         </is>
       </c>
-      <c r="J518" s="14" t="inlineStr">
+      <c r="J518" s="7" t="inlineStr">
         <is>
           <t>8840</t>
         </is>
@@ -18789,12 +18792,12 @@
           <t>7643</t>
         </is>
       </c>
-      <c r="J527" s="14" t="inlineStr">
+      <c r="J527" s="7" t="inlineStr">
         <is>
           <t>8552</t>
         </is>
       </c>
-      <c r="L527" s="14" t="inlineStr">
+      <c r="L527" s="7" t="inlineStr">
         <is>
           <t>8550</t>
         </is>
@@ -18809,7 +18812,7 @@
           <t>8733</t>
         </is>
       </c>
-      <c r="P527" s="14" t="inlineStr">
+      <c r="P527" s="7" t="inlineStr">
         <is>
           <t>6200</t>
         </is>
@@ -19300,7 +19303,7 @@
       </c>
     </row>
     <row r="542" ht="14.25" customHeight="1" s="6">
-      <c r="H542" s="7" t="inlineStr">
+      <c r="H542" s="15" t="inlineStr">
         <is>
           <t>8442</t>
         </is>
@@ -19310,7 +19313,7 @@
           <t>9422</t>
         </is>
       </c>
-      <c r="J542" s="7" t="inlineStr">
+      <c r="J542" s="15" t="inlineStr">
         <is>
           <t>9331</t>
         </is>
@@ -19325,7 +19328,7 @@
           <t>5542</t>
         </is>
       </c>
-      <c r="N542" s="7" t="inlineStr">
+      <c r="N542" s="15" t="inlineStr">
         <is>
           <t>4200</t>
         </is>
@@ -19340,7 +19343,7 @@
           <t>8765</t>
         </is>
       </c>
-      <c r="R542" s="7" t="inlineStr">
+      <c r="R542" s="15" t="inlineStr">
         <is>
           <t>6220</t>
         </is>
@@ -19882,7 +19885,7 @@
           <t>7600</t>
         </is>
       </c>
-      <c r="M554" s="14" t="inlineStr">
+      <c r="M554" s="7" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
@@ -20122,7 +20125,7 @@
           <t>6331</t>
         </is>
       </c>
-      <c r="J560" s="7" t="inlineStr">
+      <c r="J560" s="15" t="inlineStr">
         <is>
           <t>8864</t>
         </is>
@@ -20142,7 +20145,7 @@
           <t>6511</t>
         </is>
       </c>
-      <c r="P560" s="7" t="inlineStr">
+      <c r="P560" s="15" t="inlineStr">
         <is>
           <t>8220</t>
         </is>
@@ -20705,7 +20708,7 @@
           <t>6532</t>
         </is>
       </c>
-      <c r="H573" s="14" t="inlineStr">
+      <c r="H573" s="7" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
@@ -20735,7 +20738,7 @@
           <t>9800</t>
         </is>
       </c>
-      <c r="P573" s="14" t="inlineStr">
+      <c r="P573" s="7" t="inlineStr">
         <is>
           <t>7764</t>
         </is>
@@ -20915,7 +20918,7 @@
           <t>9872</t>
         </is>
       </c>
-      <c r="M579" s="7" t="inlineStr">
+      <c r="M579" s="15" t="inlineStr">
         <is>
           <t>8330</t>
         </is>
@@ -21392,7 +21395,7 @@
           <t>9740</t>
         </is>
       </c>
-      <c r="N591" s="14" t="inlineStr">
+      <c r="N591" s="7" t="inlineStr">
         <is>
           <t>7331</t>
         </is>
@@ -21713,7 +21716,7 @@
           <t>8520</t>
         </is>
       </c>
-      <c r="L600" s="14" t="inlineStr">
+      <c r="L600" s="7" t="inlineStr">
         <is>
           <t>9991</t>
         </is>
@@ -21903,7 +21906,7 @@
           <t>8755</t>
         </is>
       </c>
-      <c r="L606" s="7" t="inlineStr">
+      <c r="L606" s="15" t="inlineStr">
         <is>
           <t>9443</t>
         </is>
@@ -21918,7 +21921,7 @@
           <t>5440</t>
         </is>
       </c>
-      <c r="P606" s="7" t="inlineStr">
+      <c r="P606" s="15" t="inlineStr">
         <is>
           <t>9544</t>
         </is>
@@ -22029,7 +22032,7 @@
       </c>
     </row>
     <row r="609" ht="14.25" customHeight="1" s="6">
-      <c r="H609" s="14" t="inlineStr">
+      <c r="H609" s="7" t="inlineStr">
         <is>
           <t>8422</t>
         </is>
@@ -22064,7 +22067,7 @@
           <t>5541</t>
         </is>
       </c>
-      <c r="Q609" s="8" t="inlineStr">
+      <c r="Q609" s="7" t="inlineStr">
         <is>
           <t>8744</t>
         </is>
@@ -22224,7 +22227,7 @@
           <t>9431</t>
         </is>
       </c>
-      <c r="I615" s="7" t="inlineStr">
+      <c r="I615" s="15" t="inlineStr">
         <is>
           <t>7753</t>
         </is>
@@ -22249,7 +22252,7 @@
           <t>9732</t>
         </is>
       </c>
-      <c r="P615" s="7" t="inlineStr">
+      <c r="P615" s="15" t="inlineStr">
         <is>
           <t>8332</t>
         </is>
@@ -22375,7 +22378,7 @@
           <t>9820</t>
         </is>
       </c>
-      <c r="L618" s="14" t="inlineStr">
+      <c r="L618" s="7" t="inlineStr">
         <is>
           <t>8655</t>
         </is>
@@ -22560,7 +22563,7 @@
           <t>7542</t>
         </is>
       </c>
-      <c r="J624" s="7" t="inlineStr">
+      <c r="J624" s="15" t="inlineStr">
         <is>
           <t>7762</t>
         </is>
@@ -22575,7 +22578,7 @@
           <t>7654</t>
         </is>
       </c>
-      <c r="N624" s="7" t="inlineStr">
+      <c r="N624" s="15" t="inlineStr">
         <is>
           <t>6220</t>
         </is>
@@ -23057,7 +23060,7 @@
           <t>6210</t>
         </is>
       </c>
-      <c r="Q636" s="14" t="inlineStr">
+      <c r="Q636" s="7" t="inlineStr">
         <is>
           <t>7522</t>
         </is>
@@ -23353,7 +23356,7 @@
       </c>
     </row>
     <row r="645" ht="14.25" customHeight="1" s="6">
-      <c r="H645" s="14" t="inlineStr">
+      <c r="H645" s="7" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
@@ -23368,7 +23371,7 @@
           <t>6520</t>
         </is>
       </c>
-      <c r="L645" s="14" t="inlineStr">
+      <c r="L645" s="7" t="inlineStr">
         <is>
           <t>7311</t>
         </is>
@@ -23388,7 +23391,7 @@
           <t>9980</t>
         </is>
       </c>
-      <c r="Q645" s="14" t="inlineStr">
+      <c r="Q645" s="7" t="inlineStr">
         <is>
           <t>6631</t>
         </is>
@@ -23568,7 +23571,7 @@
           <t>8643</t>
         </is>
       </c>
-      <c r="N651" s="7" t="inlineStr">
+      <c r="N651" s="15" t="inlineStr">
         <is>
           <t>7322</t>
         </is>
@@ -23709,7 +23712,7 @@
           <t>5541</t>
         </is>
       </c>
-      <c r="N654" s="14" t="inlineStr">
+      <c r="N654" s="7" t="inlineStr">
         <is>
           <t>8442</t>
         </is>
@@ -24045,7 +24048,7 @@
           <t>7442</t>
         </is>
       </c>
-      <c r="P663" s="14" t="inlineStr">
+      <c r="P663" s="7" t="inlineStr">
         <is>
           <t>8411</t>
         </is>
@@ -24426,7 +24429,7 @@
           <t>8652</t>
         </is>
       </c>
-      <c r="E672" s="14" t="inlineStr">
+      <c r="E672" s="7" t="inlineStr">
         <is>
           <t>9953</t>
         </is>
@@ -24471,7 +24474,7 @@
           <t>9211</t>
         </is>
       </c>
-      <c r="Q672" s="14" t="inlineStr">
+      <c r="Q672" s="7" t="inlineStr">
         <is>
           <t>9663</t>
         </is>
@@ -24656,7 +24659,7 @@
           <t>5510</t>
         </is>
       </c>
-      <c r="P678" s="7" t="inlineStr">
+      <c r="P678" s="15" t="inlineStr">
         <is>
           <t>6400</t>
         </is>
@@ -25308,12 +25311,12 @@
           <t>7410</t>
         </is>
       </c>
-      <c r="M696" s="7" t="inlineStr">
+      <c r="M696" s="15" t="inlineStr">
         <is>
           <t>7751</t>
         </is>
       </c>
-      <c r="N696" s="7" t="inlineStr">
+      <c r="N696" s="15" t="inlineStr">
         <is>
           <t>9940</t>
         </is>
@@ -25449,7 +25452,7 @@
           <t>9885</t>
         </is>
       </c>
-      <c r="M699" s="14" t="inlineStr">
+      <c r="M699" s="7" t="inlineStr">
         <is>
           <t>6400</t>
         </is>
@@ -25664,7 +25667,7 @@
       </c>
     </row>
     <row r="705" ht="14.25" customHeight="1" s="6">
-      <c r="D705" s="7" t="inlineStr">
+      <c r="D705" s="15" t="inlineStr">
         <is>
           <t>9733</t>
         </is>
@@ -25714,12 +25717,12 @@
           <t>6410</t>
         </is>
       </c>
-      <c r="Q705" s="7" t="inlineStr">
+      <c r="Q705" s="15" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="R705" s="7" t="inlineStr">
+      <c r="R705" s="15" t="inlineStr">
         <is>
           <t>6640</t>
         </is>
@@ -25845,7 +25848,7 @@
           <t>8876</t>
         </is>
       </c>
-      <c r="F708" s="14" t="inlineStr">
+      <c r="F708" s="7" t="inlineStr">
         <is>
           <t>6653</t>
         </is>
@@ -25865,7 +25868,7 @@
           <t>7765</t>
         </is>
       </c>
-      <c r="L708" s="14" t="inlineStr">
+      <c r="L708" s="7" t="inlineStr">
         <is>
           <t>3100</t>
         </is>
@@ -26065,7 +26068,7 @@
           <t>9833</t>
         </is>
       </c>
-      <c r="N714" s="7" t="inlineStr">
+      <c r="N714" s="15" t="inlineStr">
         <is>
           <t>8831</t>
         </is>
@@ -26196,7 +26199,7 @@
           <t>7662</t>
         </is>
       </c>
-      <c r="L717" s="14" t="inlineStr">
+      <c r="L717" s="7" t="inlineStr">
         <is>
           <t>6655</t>
         </is>
@@ -26376,7 +26379,7 @@
           <t>9743</t>
         </is>
       </c>
-      <c r="I723" s="7" t="inlineStr">
+      <c r="I723" s="8" t="inlineStr">
         <is>
           <t>9855</t>
         </is>
@@ -26512,7 +26515,7 @@
       </c>
     </row>
     <row r="726" ht="14.25" customHeight="1" s="6">
-      <c r="H726" s="14" t="inlineStr">
+      <c r="H726" s="7" t="inlineStr">
         <is>
           <t>7775</t>
         </is>
@@ -26742,7 +26745,7 @@
           <t>8210</t>
         </is>
       </c>
-      <c r="R732" s="7" t="inlineStr">
+      <c r="R732" s="15" t="inlineStr">
         <is>
           <t>7511</t>
         </is>
@@ -27058,12 +27061,12 @@
           <t>6510</t>
         </is>
       </c>
-      <c r="N741" s="7" t="inlineStr">
+      <c r="N741" s="15" t="inlineStr">
         <is>
           <t>8644</t>
         </is>
       </c>
-      <c r="P741" s="7" t="inlineStr">
+      <c r="P741" s="15" t="inlineStr">
         <is>
           <t>9443</t>
         </is>
@@ -27184,7 +27187,7 @@
           <t>8320</t>
         </is>
       </c>
-      <c r="J744" s="14" t="inlineStr">
+      <c r="J744" s="7" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
@@ -27389,7 +27392,7 @@
           <t>6643</t>
         </is>
       </c>
-      <c r="N750" s="7" t="inlineStr">
+      <c r="N750" s="15" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
@@ -27399,12 +27402,12 @@
           <t>6430</t>
         </is>
       </c>
-      <c r="Q750" s="7" t="inlineStr">
+      <c r="Q750" s="15" t="inlineStr">
         <is>
           <t>7311</t>
         </is>
       </c>
-      <c r="R750" s="7" t="inlineStr">
+      <c r="R750" s="15" t="inlineStr">
         <is>
           <t>7331</t>
         </is>
@@ -27515,7 +27518,7 @@
           <t>8844</t>
         </is>
       </c>
-      <c r="J753" s="14" t="inlineStr">
+      <c r="J753" s="7" t="inlineStr">
         <is>
           <t>7311</t>
         </is>
@@ -27720,7 +27723,7 @@
           <t>6542</t>
         </is>
       </c>
-      <c r="N759" s="7" t="inlineStr">
+      <c r="N759" s="8" t="inlineStr">
         <is>
           <t>9550</t>
         </is>
@@ -27735,7 +27738,7 @@
           <t>7610</t>
         </is>
       </c>
-      <c r="R759" s="7" t="inlineStr">
+      <c r="R759" s="8" t="inlineStr">
         <is>
           <t>7550</t>
         </is>
@@ -27876,7 +27879,7 @@
           <t>7410</t>
         </is>
       </c>
-      <c r="R762" s="14" t="inlineStr">
+      <c r="R762" s="7" t="inlineStr">
         <is>
           <t>9663</t>
         </is>
@@ -28177,7 +28180,7 @@
           <t>7542</t>
         </is>
       </c>
-      <c r="J771" s="14" t="inlineStr">
+      <c r="J771" s="7" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
@@ -28197,7 +28200,7 @@
           <t>8860</t>
         </is>
       </c>
-      <c r="P771" s="14" t="inlineStr">
+      <c r="P771" s="7" t="inlineStr">
         <is>
           <t>6433</t>
         </is>
@@ -28513,7 +28516,7 @@
           <t>8864</t>
         </is>
       </c>
-      <c r="L780" s="14" t="inlineStr">
+      <c r="L780" s="7" t="inlineStr">
         <is>
           <t>8411</t>
         </is>
@@ -28533,7 +28536,7 @@
           <t>7430</t>
         </is>
       </c>
-      <c r="Q780" s="14" t="inlineStr">
+      <c r="Q780" s="7" t="inlineStr">
         <is>
           <t>7441</t>
         </is>
@@ -28924,12 +28927,12 @@
           <t>9820</t>
         </is>
       </c>
-      <c r="I789" s="14" t="inlineStr">
+      <c r="I789" s="7" t="inlineStr">
         <is>
           <t>5520</t>
         </is>
       </c>
-      <c r="J789" s="14" t="inlineStr">
+      <c r="J789" s="7" t="inlineStr">
         <is>
           <t>7751</t>
         </is>
@@ -29275,7 +29278,7 @@
           <t>9871</t>
         </is>
       </c>
-      <c r="N798" s="14" t="inlineStr">
+      <c r="N798" s="7" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
@@ -29591,7 +29594,7 @@
           <t>7410</t>
         </is>
       </c>
-      <c r="J807" s="14" t="inlineStr">
+      <c r="J807" s="7" t="inlineStr">
         <is>
           <t>8442</t>
         </is>
@@ -29952,7 +29955,7 @@
           <t>6661</t>
         </is>
       </c>
-      <c r="R816" s="8" t="inlineStr">
+      <c r="R816" s="7" t="inlineStr">
         <is>
           <t>7440</t>
         </is>
@@ -41583,7 +41586,7 @@
       <c r="E1123" s="10" t="n"/>
       <c r="F1123" s="10" t="n"/>
       <c r="G1123" s="10" t="n"/>
-      <c r="H1123" s="10" t="n">
+      <c r="H1123" s="13" t="n">
         <v>8550</v>
       </c>
       <c r="I1123" s="10" t="n">
@@ -41593,7 +41596,7 @@
         <v>5443</v>
       </c>
       <c r="K1123" s="10" t="n"/>
-      <c r="L1123" s="10" t="n">
+      <c r="L1123" s="14" t="n">
         <v>9550</v>
       </c>
       <c r="M1123" s="10" t="n">
@@ -41725,7 +41728,7 @@
       <c r="L1126" s="10" t="n">
         <v>9753</v>
       </c>
-      <c r="M1126" s="13" t="n">
+      <c r="M1126" s="10" t="n">
         <v>9744</v>
       </c>
       <c r="N1126" s="10" t="n">
